--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 73 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 71 clubs short</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2052,8 +2052,8 @@
       <c r="S14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T14" s="9" t="n">
-        <v>0</v>
+      <c r="T14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2349,11 +2349,11 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W17" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W17" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>4</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2446,11 +2446,11 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>0</v>
+      <c r="V18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>7</v>
@@ -2458,8 +2458,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W25" s="9" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3496,16 +3496,16 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="9" t="n">
-        <v>1</v>
+      <c r="S29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T29" s="9" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3889,8 +3889,8 @@
       <c r="Q33" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R33" s="9" t="n">
-        <v>1</v>
+      <c r="R33" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S33" s="9" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>1</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6144,8 +6144,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>1</v>
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="P108" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q108" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R108" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>2</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13301,8 +13301,8 @@
       <c r="R130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S130" s="9" t="n">
-        <v>1</v>
+      <c r="S130" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T130" s="10" t="n">
         <v>1</v>
@@ -13995,8 +13995,8 @@
       <c r="W137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X137" s="9" t="n">
-        <v>3</v>
+      <c r="X137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="8" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>0</v>
@@ -15520,7 +15520,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -15553,7 +15553,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15619,7 +15619,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -15652,7 +15652,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -15784,7 +15784,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -16213,13 +16213,13 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>

--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 71 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 70 clubs short</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1279,8 +1279,8 @@
       <c r="T6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
+      <c r="U6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V6" s="10" t="n">
         <v>4</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2437,8 +2437,8 @@
       <c r="R18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="9" t="n">
-        <v>1</v>
+      <c r="S18" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T18" s="9" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3222,11 +3222,11 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>0</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" s="10" t="n">
         <v>7</v>
@@ -3408,13 +3408,13 @@
         <v>2</v>
       </c>
       <c r="S28" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="T28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="V28" s="10" t="n">
         <v>4</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3693,7 +3693,7 @@
         <v>2</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>0</v>
@@ -3704,8 +3704,8 @@
       <c r="T31" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U31" s="9" t="n">
-        <v>0</v>
+      <c r="U31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V31" s="10" t="n">
         <v>4</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>1</v>
@@ -10480,13 +10480,13 @@
         </is>
       </c>
       <c r="P101" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q101" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R101" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S101" s="9" t="n">
         <v>1</v>
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="P108" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q108" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R108" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>2</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14068,14 +14068,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P138" s="9" t="n">
-        <v>3</v>
+      <c r="P138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q138" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R138" s="9" t="n">
-        <v>1</v>
+      <c r="R138" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S138" s="10" t="n">
         <v>2</v>
@@ -15454,7 +15454,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15553,13 +15553,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -15586,7 +15586,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15619,7 +15619,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -16279,7 +16279,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>

--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 70 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
@@ -1003,8 +1003,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1197,8 +1197,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1294,8 +1294,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1973,8 +1973,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3028,11 +3028,11 @@
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="9" t="n">
-        <v>0</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W24" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>5</v>
@@ -3040,8 +3040,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3275,17 +3275,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
@@ -3319,11 +3319,11 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>3</v>
+      <c r="V27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>4</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3698,8 +3698,8 @@
       <c r="R31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="9" t="n">
-        <v>1</v>
+      <c r="S31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T31" s="10" t="n">
         <v>1</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3816,8 +3816,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -3998,11 +3998,11 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>0</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -4010,8 +4010,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="10" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4107,8 +4107,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="10" t="n">
         <v>2</v>
@@ -4390,7 +4390,7 @@
         <v>4</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>7</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4465,8 +4465,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P39" s="9" t="n">
-        <v>1</v>
+      <c r="P39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>1</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5021,17 +5021,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
@@ -5048,7 +5048,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" s="9" t="n">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" s="9" t="n">
         <v>0</v>
@@ -5065,11 +5065,11 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>0</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>5</v>
@@ -5077,8 +5077,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q48" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
@@ -5445,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5550,11 +5550,11 @@
       <c r="U50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="9" t="n">
-        <v>0</v>
+      <c r="V50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>5</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5639,7 +5639,7 @@
         <v>1</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" s="9" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6047,8 +6047,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7017,8 +7017,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7987,8 +7987,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8278,8 +8278,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8569,8 +8569,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9219,16 +9219,16 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" s="10" t="n">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="P101" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q101" s="10" t="n">
         <v>2</v>
@@ -10509,8 +10509,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -10683,7 +10683,7 @@
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T103" s="9" t="n">
         <v>0</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -10897,8 +10897,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11061,8 +11061,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P107" s="9" t="n">
-        <v>1</v>
+      <c r="P107" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -11159,13 +11159,13 @@
         </is>
       </c>
       <c r="P108" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q108" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R108" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S108" s="10" t="n">
         <v>2</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11255,8 +11255,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P109" s="9" t="n">
-        <v>3</v>
+      <c r="P109" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11576,8 +11576,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12449,8 +12449,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12740,8 +12740,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>1</v>
@@ -13314,7 +13314,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>7</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13904,8 +13904,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -14377,11 +14377,11 @@
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W141" s="9" t="n">
-        <v>0</v>
+      <c r="V141" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W141" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X141" s="10" t="n">
         <v>7</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15454,7 +15454,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15487,7 +15487,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15520,7 +15520,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -15586,7 +15586,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15601,7 +15601,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -15619,13 +15619,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -15652,7 +15652,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>3.17</v>
+        <v>3.67</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -15685,7 +15685,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15718,7 +15718,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -15733,7 +15733,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -15751,7 +15751,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15784,7 +15784,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -15850,7 +15850,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -15916,7 +15916,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15949,7 +15949,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15982,7 +15982,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -16048,7 +16048,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -16081,7 +16081,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -16114,7 +16114,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -16180,7 +16180,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16213,7 +16213,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -16279,7 +16279,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -16312,7 +16312,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -12,8 +12,8 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$152</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA152"/>
+  <dimension ref="A1:AA153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="P2" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="9" t="n">
         <v>1</v>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="P4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1432,17 +1432,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-34</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>12</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M8" s="7" t="n">
@@ -1476,11 +1476,11 @@
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" s="9" t="n">
-        <v>0</v>
+      <c r="V8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W8" s="10" t="n">
+        <v>24</v>
       </c>
       <c r="X8" s="10" t="n">
         <v>5</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1626,17 +1626,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M10" s="7" t="n">
@@ -1670,11 +1670,11 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>0</v>
+      <c r="V10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>EisenAmper Toastmasters Club</t>
+          <t>EisnerAmper Toastmasters Club</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3207,8 +3207,8 @@
       <c r="P26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q26" s="9" t="n">
-        <v>1</v>
+      <c r="Q26" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R26" s="9" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3275,17 +3275,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M27" s="7" t="n">
@@ -3322,8 +3322,8 @@
       <c r="V27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W27" s="9" t="n">
-        <v>1</v>
+      <c r="W27" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3693,7 +3693,7 @@
         <v>4</v>
       </c>
       <c r="Q31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="9" t="n">
         <v>0</v>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="P37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="9" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4389,8 +4389,8 @@
       <c r="V38" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W38" s="9" t="n">
-        <v>1</v>
+      <c r="W38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>7</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="10" t="n">
         <v>2</v>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4580,8 +4580,8 @@
       <c r="U40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="9" t="n">
-        <v>3</v>
+      <c r="V40" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>6</v>
@@ -5827,7 +5827,7 @@
         <v>3</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="P58" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q58" s="10" t="n">
         <v>2</v>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q61" s="9" t="n">
         <v>0</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="S69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="10" t="n">
         <v>1</v>
@@ -7397,7 +7397,7 @@
         <v>4</v>
       </c>
       <c r="W69" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X69" s="10" t="n">
         <v>4</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8169,11 +8169,11 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="9" t="n">
-        <v>0</v>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>4</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>5</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9033,8 +9033,8 @@
       <c r="R86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="9" t="n">
-        <v>1</v>
+      <c r="S86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T86" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L91" s="8" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>6</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>0</v>
@@ -10010,7 +10010,7 @@
         <v>1</v>
       </c>
       <c r="U96" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V96" s="10" t="n">
         <v>4</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10585,8 +10585,8 @@
       <c r="R102" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="S102" s="9" t="n">
-        <v>1</v>
+      <c r="S102" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T102" s="9" t="n">
         <v>0</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-31</v>
-      </c>
-      <c r="L103" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M103" s="7" t="n">
@@ -10691,11 +10691,11 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" s="9" t="n">
-        <v>0</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W103" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>7</v>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>1</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11267,8 +11267,8 @@
       <c r="S109" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T109" s="9" t="n">
-        <v>0</v>
+      <c r="T109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
@@ -11277,7 +11277,7 @@
         <v>4</v>
       </c>
       <c r="W109" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11295,20 +11295,20 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>3572259</v>
+        <v>28681070</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>First Aureate</t>
+          <t>Talk Masters Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11326,17 +11326,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L110" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M110" s="7" t="n">
@@ -11352,8 +11352,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P110" s="10" t="n">
-        <v>9</v>
+      <c r="P110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -11376,17 +11376,17 @@
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="10" t="n">
-        <v>5</v>
+      <c r="X110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -11401,11 +11401,11 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>9496</v>
+        <v>3572259</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>LA Nineteen Twenty-Four Club</t>
+          <t>First Aureate</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -11423,17 +11423,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L111" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="7" t="n">
@@ -11449,11 +11449,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P111" s="9" t="n">
-        <v>1</v>
+      <c r="P111" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -11468,19 +11468,19 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X111" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="10" t="n">
-        <v>1</v>
+      <c r="Z111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -11498,15 +11498,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>7747857</v>
+        <v>9496</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Samvaad@FICO</t>
+          <t>LA Nineteen Twenty-Four Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,17 +11520,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L112" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M112" s="7" t="n">
@@ -11550,7 +11550,7 @@
         <v>2</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -11564,14 +11564,14 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>1</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X112" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -11595,11 +11595,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>2721508</v>
+        <v>7747857</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Speakers' Den</t>
+          <t>Samvaad@FICO</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -11620,10 +11620,10 @@
         <v>8</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L113" s="8" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -11662,13 +11662,13 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -11692,15 +11692,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28676476</v>
+        <v>2721508</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>The Gabbys Online Advanced Toastmasters Club</t>
+          <t>Speakers' Den</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="L114" s="8" t="inlineStr">
         <is>
@@ -11740,8 +11740,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P114" s="10" t="n">
-        <v>4</v>
+      <c r="P114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -11749,20 +11749,20 @@
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V114" s="10" t="n">
-        <v>4</v>
+      <c r="S114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
         <v>4</v>
@@ -11789,15 +11789,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>3078424</v>
+        <v>28676476</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Indiranagar Pride</t>
+          <t>The Gabbys Online Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,17 +11811,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L115" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="7" t="n">
@@ -11837,32 +11837,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P115" s="9" t="n">
+      <c r="P115" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q115" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" s="10" t="n">
         <v>3</v>
-      </c>
-      <c r="Q115" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="V115" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W115" s="10" t="n">
-        <v>8</v>
+      <c r="W115" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -11882,19 +11882,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>7235902</v>
+        <v>3078424</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Airbus India Toastmasters Club</t>
+          <t>Toastmasters Indiranagar Pride</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,17 +11908,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-31</v>
-      </c>
-      <c r="L116" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="7" t="n">
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -11955,11 +11955,11 @@
       <c r="V116" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W116" s="9" t="n">
-        <v>1</v>
+      <c r="W116" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -11983,11 +11983,11 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>28677014</v>
+        <v>7235902</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Amazon Bangalore Toastmasters Club</t>
+          <t>Airbus India Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
@@ -12005,17 +12005,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-31</v>
+      </c>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="7" t="n">
@@ -12035,7 +12035,7 @@
         <v>1</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12043,8 +12043,8 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U117" s="9" t="n">
         <v>0</v>
@@ -12052,8 +12052,8 @@
       <c r="V117" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W117" s="10" t="n">
-        <v>9</v>
+      <c r="W117" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X117" s="10" t="n">
         <v>6</v>
@@ -12080,15 +12080,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1548643</v>
+        <v>28677014</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Express2Lead Toastmasters Club</t>
+          <t>Amazon Bangalore Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J118" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J118" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="K118" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L118" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M118" s="7" t="n">
@@ -12146,14 +12146,14 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W118" s="9" t="n">
-        <v>0</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W118" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28678398</v>
+        <v>1548643</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>EY CT Bangalore Toastmasters Club</t>
+          <t>Express2Lead Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="L119" s="8" t="inlineStr">
         <is>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12243,20 +12243,20 @@
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="9" t="n">
-        <v>0</v>
+      <c r="V119" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="9" t="n">
-        <v>0</v>
+      <c r="X119" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -12274,15 +12274,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28680272</v>
+        <v>28678398</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>GE Vernova Toastmasters Club</t>
+          <t>EY CT Bangalore Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12296,17 +12296,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L120" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
@@ -12340,20 +12340,20 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W120" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="X120" s="10" t="n">
-        <v>6</v>
+      <c r="V120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="10" t="n">
-        <v>1</v>
+      <c r="Z120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -12371,15 +12371,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>2177847</v>
+        <v>28680272</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Thomson Reuters Toastmasters Club Bangalore</t>
+          <t>GE Vernova Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,25 +12393,25 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>15</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M121" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O121" s="8" t="inlineStr">
@@ -12437,23 +12437,23 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" s="9" t="n">
-        <v>0</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W121" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="X121" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA121" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -12464,19 +12464,19 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28677844</v>
+        <v>2177847</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>BSH Toastmasters Club</t>
+          <t>Thomson Reuters Toastmasters Club Bangalore</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12490,25 +12490,25 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O122" s="8" t="inlineStr">
@@ -12516,11 +12516,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P122" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q122" s="10" t="n">
-        <v>2</v>
+      <c r="P122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -12528,29 +12528,29 @@
       <c r="S122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="10" t="n">
-        <v>1</v>
+      <c r="T122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W122" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="X122" s="10" t="n">
-        <v>6</v>
+      <c r="V122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA122" s="10" t="n">
-        <v>1</v>
+      <c r="Z122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1134620</v>
+        <v>28677844</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Capgemini Toastmasters Club</t>
+          <t>BSH Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12587,17 +12587,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M123" s="7" t="n">
@@ -12613,11 +12613,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" s="9" t="n">
-        <v>0</v>
+      <c r="P123" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q123" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -12625,26 +12625,26 @@
       <c r="S123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W123" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
@@ -12662,15 +12662,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>1364680</v>
+        <v>1134620</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar Bangalore RMZ Toastmasters Club</t>
+          <t>Capgemini Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,17 +12684,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -12711,10 +12711,10 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
@@ -12722,26 +12722,26 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="10" t="n">
-        <v>1</v>
+      <c r="T124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W124" s="10" t="n">
-        <v>5</v>
+      <c r="V124" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="10" t="n">
-        <v>1</v>
+      <c r="Z124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>4885652</v>
+        <v>1364680</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Qonverse</t>
+          <t>Caterpillar Bangalore RMZ Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,17 +12781,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L125" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M125" s="7" t="n">
@@ -12808,31 +12808,31 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T125" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W125" s="9" t="n">
-        <v>0</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W125" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>3958529</v>
+        <v>4885652</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>SAP SpeakToLead Toastmasters Club</t>
+          <t>Qonverse</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,17 +12878,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -12914,22 +12914,22 @@
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T126" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="10" t="n">
-        <v>4</v>
+      <c r="V126" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -12949,19 +12949,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>7476590</v>
+        <v>3958529</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Boeing Bangalore Toastmasters Club</t>
+          <t>SAP SpeakToLead Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -12975,17 +12975,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="K127" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="L127" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M127" s="7" t="n">
@@ -13002,10 +13002,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13013,17 +13013,17 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>1</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X127" s="10" t="n">
         <v>7</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28678245</v>
+        <v>7476590</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Elite Orators Toastmasters Club</t>
+          <t>Boeing Bangalore Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L128" s="8" t="inlineStr">
         <is>
@@ -13099,10 +13099,10 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -13117,19 +13117,19 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="9" t="n">
-        <v>1</v>
+      <c r="X128" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13147,15 +13147,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28675747</v>
+        <v>28678245</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Gspeaks Toastmasters Club</t>
+          <t>Elite Orators Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,17 +13169,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="7" t="n">
@@ -13213,20 +13213,20 @@
       <c r="U129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="10" t="n">
-        <v>4</v>
+      <c r="V129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W129" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X129" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X129" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="10" t="n">
-        <v>1</v>
+      <c r="Z129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13244,15 +13244,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>5840831</v>
+        <v>28675747</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>HPE Networking India Toastmasters Club</t>
+          <t>Gspeaks Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13266,17 +13266,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L130" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M130" s="7" t="n">
@@ -13293,16 +13293,16 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q130" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T130" s="9" t="n">
         <v>0</v>
@@ -13310,14 +13310,14 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W130" s="9" t="n">
-        <v>0</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X130" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -13341,15 +13341,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>7845315</v>
+        <v>5840831</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>NVIDIA International Toastmasters</t>
+          <t>HPE Networking India Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="L131" s="8" t="inlineStr">
         <is>
@@ -13390,28 +13390,28 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q131" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q131" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="T131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V131" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X131" s="10" t="n">
         <v>7</v>
@@ -13429,24 +13429,24 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>7422548</v>
+        <v>7845315</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Analog Devices India Toastmasters Club</t>
+          <t>NVIDIA International Toastmasters</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,17 +13460,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="7" t="n">
@@ -13490,25 +13490,25 @@
         <v>2</v>
       </c>
       <c r="Q132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" s="9" t="n">
-        <v>0</v>
+      <c r="S132" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V132" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W132" s="10" t="n">
-        <v>29</v>
+      <c r="W132" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>7</v>
@@ -13535,15 +13535,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28678119</v>
+        <v>7422548</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>GT Indus India Toastmasters Club</t>
+          <t>Analog Devices India Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,25 +13557,25 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>50</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-50</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>13</v>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O133" s="8" t="inlineStr">
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -13601,23 +13601,23 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" s="9" t="n">
-        <v>0</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W133" s="10" t="n">
+        <v>29</v>
       </c>
       <c r="X133" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" s="9" t="n">
-        <v>0</v>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -13632,15 +13632,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>863230</v>
+        <v>28678119</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>IBM Synergy Toastmasters Club</t>
+          <t>GT Indus India Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13668,11 +13668,11 @@
         </is>
       </c>
       <c r="M134" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O134" s="8" t="inlineStr">
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>0</v>
@@ -13690,7 +13690,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T134" s="9" t="n">
         <v>0</v>
@@ -13698,23 +13698,23 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="10" t="n">
-        <v>4</v>
+      <c r="V134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA134" s="10" t="n">
-        <v>1</v>
+      <c r="Z134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>5359247</v>
+        <v>863230</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Kaggadasapura Toastmasters Club</t>
+          <t>IBM Synergy Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>0</v>
       </c>
       <c r="S135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T135" s="9" t="n">
         <v>0</v>
@@ -13795,11 +13795,11 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>1</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>4</v>
@@ -13807,8 +13807,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -13826,15 +13826,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>5843268</v>
+        <v>5359247</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Rock the Talk</t>
+          <t>Kaggadasapura Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,17 +13848,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="7" t="n">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
         <v>0</v>
@@ -13892,20 +13892,20 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="10" t="n">
+      <c r="V136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X136" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="10" t="n">
-        <v>1</v>
+      <c r="Z136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -13919,15 +13919,15 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>4785827</v>
+        <v>5843268</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>FMRI EGL - Movers &amp; Speakers Toastmasters Club</t>
+          <t>Rock the Talk</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="K137" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L137" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M137" s="7" t="n">
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="S137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T137" s="9" t="n">
         <v>0</v>
@@ -13993,7 +13993,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>1540185</v>
+        <v>4785827</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Focus Talk Toastmasters</t>
+          <t>FMRI EGL - Movers &amp; Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L138" s="8" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>0</v>
       </c>
       <c r="S138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T138" s="9" t="n">
         <v>0</v>
@@ -14086,20 +14086,20 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>2</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14117,15 +14117,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>7751850</v>
+        <v>1540185</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Lam Research India Toastmasters Club</t>
+          <t>Focus Talk Toastmasters</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,17 +14139,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L139" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="7" t="n">
@@ -14165,38 +14165,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P139" s="10" t="n">
+      <c r="P139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q139" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R139" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S139" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T139" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U139" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V139" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W139" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X139" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="10" t="n">
-        <v>1</v>
+      <c r="Z139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -14214,15 +14214,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>7179851</v>
+        <v>7751850</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>SwaR Toastmasters</t>
+          <t>Lam Research India Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K140" s="4" t="n">
         <v>-12</v>
       </c>
-      <c r="L140" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M140" s="7" t="n">
@@ -14262,38 +14262,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" s="9" t="n">
+      <c r="P140" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q140" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W140" s="9" t="n">
-        <v>0</v>
+      <c r="R140" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S140" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U140" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V140" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W140" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X140" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -14311,15 +14311,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>28679155</v>
+        <v>7179851</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>UKG Toastmasters Bangalore</t>
+          <t>SwaR Toastmasters</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
@@ -14377,14 +14377,14 @@
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="10" t="n">
-        <v>4</v>
+      <c r="V141" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -14404,19 +14404,19 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>28679016</v>
+        <v>28679155</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>CHII Toastmasters Club</t>
+          <t>UKG Toastmasters Bangalore</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -14430,17 +14430,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="7" t="n">
@@ -14477,17 +14477,17 @@
       <c r="V142" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W142" s="10" t="n">
-        <v>9</v>
+      <c r="W142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="10" t="n">
-        <v>1</v>
+      <c r="Z142" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -14505,15 +14505,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>28680644</v>
+        <v>28679016</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>DP World Toastmasters Club</t>
+          <t>CHII Toastmasters Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14571,20 +14571,20 @@
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X143" s="9" t="n">
-        <v>0</v>
+      <c r="V143" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W143" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="X143" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA143" s="10" t="n">
         <v>1</v>
@@ -14602,11 +14602,11 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>28677461</v>
+        <v>28680644</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>IGrow India Leaders</t>
+          <t>DP World Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
@@ -14624,17 +14624,17 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M144" s="7" t="n">
@@ -14651,7 +14651,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -14674,8 +14674,8 @@
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X144" s="10" t="n">
-        <v>7</v>
+      <c r="X144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>28677658</v>
+        <v>28677461</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Opentext Toastmasters Club</t>
+          <t>IGrow India Leaders</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,17 +14721,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M145" s="7" t="n">
@@ -14748,28 +14748,28 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q145" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T145" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U145" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V145" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W145" s="9" t="n">
-        <v>2</v>
+      <c r="W145" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X145" s="10" t="n">
         <v>7</v>
@@ -14777,8 +14777,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="10" t="n">
-        <v>1</v>
+      <c r="Z145" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -14796,15 +14796,15 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>28678476</v>
+        <v>28677658</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>PANIndia Toastmasters Club</t>
+          <t>Opentext Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="L146" s="8" t="inlineStr">
         <is>
@@ -14845,22 +14845,22 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V146" s="10" t="n">
         <v>4</v>
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>28677605</v>
+        <v>28678476</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Volvo Vocalizers</t>
+          <t>PANIndia Toastmasters Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-27</v>
+        <v>-2</v>
       </c>
       <c r="L147" s="8" t="inlineStr">
         <is>
@@ -14959,20 +14959,20 @@
       <c r="U147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W147" s="9" t="n">
-        <v>0</v>
+      <c r="V147" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X147" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -14986,15 +14986,15 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>5998569</v>
+        <v>28677605</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>BMC Bengaluru Toastmasters Club</t>
+          <t>Volvo Vocalizers</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-2</v>
+        <v>-27</v>
       </c>
       <c r="L148" s="8" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15087,15 +15087,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>2102647</v>
+        <v>5998569</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Dell Sukti Toastmasters Club</t>
+          <t>BMC Bengaluru Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="L149" s="8" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -15154,19 +15154,19 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X149" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z149" s="10" t="n">
-        <v>1</v>
+      <c r="Z149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA149" s="10" t="n">
         <v>1</v>
@@ -15184,15 +15184,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>28678960</v>
+        <v>2102647</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Eloquent Voices of CME Group</t>
+          <t>Dell Sukti Toastmasters Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="7" t="n">
@@ -15233,10 +15233,10 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q150" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q150" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
@@ -15250,14 +15250,14 @@
       <c r="U150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="10" t="n">
+      <c r="V150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W150" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X150" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
@@ -15281,15 +15281,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>28677875</v>
+        <v>28678960</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Open Text Toastmasters Club, BTP</t>
+          <t>Eloquent Voices of CME Group</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15303,17 +15303,17 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L151" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M151" s="7" t="n">
@@ -15330,10 +15330,10 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q151" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q151" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
@@ -15341,20 +15341,20 @@
       <c r="S151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T151" s="10" t="n">
-        <v>1</v>
+      <c r="T151" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V151" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W151" s="9" t="n">
-        <v>0</v>
+      <c r="V151" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W151" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X151" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
@@ -15378,11 +15378,11 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>7306349</v>
+        <v>28677875</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Salesforce Bangalore Toastmasters Club</t>
+          <t>Open Text Toastmasters Club, BTP</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -15400,17 +15400,17 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L152" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M152" s="7" t="n">
@@ -15427,10 +15427,10 @@
         </is>
       </c>
       <c r="P152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q152" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R152" s="9" t="n">
         <v>0</v>
@@ -15445,26 +15445,123 @@
         <v>0</v>
       </c>
       <c r="V152" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W152" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X152" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y152" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA152" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="n">
+        <v>7306349</v>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Salesforce Bangalore Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G153" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K153" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M153" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O153" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="Y152" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z152" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA152" s="10" t="n">
+      <c r="Y153" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA153" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA152"/>
+  <autoFilter ref="A1:AA153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15475,7 +15572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -15584,7 +15681,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15599,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -15683,7 +15780,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15698,7 +15795,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -15749,7 +15846,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -15782,7 +15879,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -16013,7 +16110,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16046,7 +16143,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16145,22 +16242,22 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>4</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -16178,7 +16275,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -16199,25 +16296,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -16226,7 +16323,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -16237,26 +16334,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
@@ -16270,29 +16367,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -16303,14 +16400,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -16325,40 +16422,40 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -16369,29 +16466,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -16402,20 +16499,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -16424,7 +16521,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -16435,33 +16532,66 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>04</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C30" t="n">
         <v>5</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>1.8</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>5</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I29"/>
+  <autoFilter ref="A1:I30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/228/inyear.xlsx
+++ b/docs/d/228/inyear.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$153</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 41 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
         <v>2</v>
       </c>
       <c r="Q4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="9" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -5539,7 +5539,7 @@
         <v>2</v>
       </c>
       <c r="R50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" s="9" t="n">
         <v>1</v>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5826,8 +5826,8 @@
       <c r="P53" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q53" s="9" t="n">
-        <v>1</v>
+      <c r="Q53" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6793,8 +6793,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P63" s="9" t="n">
-        <v>2</v>
+      <c r="P63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>1</v>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="10" t="n">
         <v>2</v>
@@ -8322,10 +8322,10 @@
         <v>15</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L89" s="8" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>1</v>
@@ -9521,8 +9521,8 @@
       <c r="S91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T91" s="9" t="n">
-        <v>0</v>
+      <c r="T91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U91" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>4</v>
       </c>
       <c r="W93" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X93" s="10" t="n">
         <v>6</v>
@@ -10140,15 +10140,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>5404217</v>
+        <v>28681070</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Travelators</t>
+          <t>Talk Masters Toastmasters Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L98" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M98" s="7" t="n">
@@ -10212,17 +10212,17 @@
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="10" t="n">
-        <v>4</v>
+      <c r="X98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -10233,19 +10233,19 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>28678954</v>
+        <v>5404217</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar GFSD TM Club</t>
+          <t>Travelators</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10259,17 +10259,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="7" t="n">
@@ -10286,7 +10286,7 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q99" s="9" t="n">
         <v>0</v>
@@ -10294,29 +10294,29 @@
       <c r="R99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S99" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T99" s="10" t="n">
-        <v>1</v>
+      <c r="S99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W99" s="10" t="n">
-        <v>9</v>
+      <c r="V99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X99" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="10" t="n">
-        <v>1</v>
+      <c r="Z99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -10334,15 +10334,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>28677639</v>
+        <v>28678954</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>CELO Toastmasters</t>
+          <t>Caterpillar GFSD TM Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,17 +10356,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L100" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M100" s="7" t="n">
@@ -10383,7 +10383,7 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -10391,29 +10391,29 @@
       <c r="R100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" s="9" t="n">
-        <v>0</v>
+      <c r="S100" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X100" s="9" t="n">
-        <v>0</v>
+      <c r="V100" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W100" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X100" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -10431,11 +10431,11 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28680641</v>
+        <v>28677639</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>PHINIA Toastmasters Club</t>
+          <t>CELO Toastmasters</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -10453,17 +10453,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="7" t="n">
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -10503,8 +10503,8 @@
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="10" t="n">
-        <v>7</v>
+      <c r="X101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -10528,15 +10528,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>28675418</v>
+        <v>28680641</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Talking Titans Toastmasters Club</t>
+          <t>PHINIA Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
@@ -10576,38 +10576,38 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P102" s="10" t="n">
+      <c r="P102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Q102" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R102" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S102" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W102" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="X102" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="10" t="n">
-        <v>1</v>
+      <c r="Z102" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -10625,15 +10625,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>28677952</v>
+        <v>28675418</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>TE Connectivity Sahasra Shree Toastmasters Club</t>
+          <t>Talking Titans Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -10673,18 +10673,18 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P103" s="9" t="n">
-        <v>1</v>
+      <c r="P103" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Q103" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R103" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S103" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S103" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="T103" s="10" t="n">
         <v>1</v>
       </c>
@@ -10695,16 +10695,16 @@
         <v>4</v>
       </c>
       <c r="W103" s="10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="X103" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28676833</v>
+        <v>28677952</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Wissen Bangalore Toastmasters Club</t>
+          <t>TE Connectivity Sahasra Shree Toastmasters Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,17 +10744,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M104" s="7" t="n">
@@ -10771,37 +10771,37 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" s="9" t="n">
-        <v>0</v>
+      <c r="R104" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T104" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" s="9" t="n">
-        <v>0</v>
+      <c r="V104" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W104" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X104" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="10" t="n">
-        <v>1</v>
+      <c r="Z104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10815,15 +10815,15 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28678926</v>
+        <v>28676833</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>AVK India Toastmasters Club</t>
+          <t>Wissen Bangalore Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -10877,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="9" t="n">
         <v>0</v>
@@ -10892,13 +10892,13 @@
         <v>0</v>
       </c>
       <c r="X105" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z105" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -10916,15 +10916,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>7310596</v>
+        <v>28678926</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Koch Toastmasters Club</t>
+          <t>AVK India Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-22</v>
+        <v>-12</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -10965,37 +10965,37 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z106" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11013,15 +11013,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28676864</v>
+        <v>7310596</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Novo Nordisk Toastmasters Club</t>
+          <t>Koch Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11062,10 +11062,10 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11073,8 +11073,8 @@
       <c r="S107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U107" s="9" t="n">
         <v>0</v>
@@ -11085,8 +11085,8 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="9" t="n">
-        <v>0</v>
+      <c r="X107" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28679487</v>
+        <v>28676864</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>o9 Toastmasters Club</t>
+          <t>Novo Nordisk Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="7" t="n">
@@ -11158,8 +11158,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P108" s="10" t="n">
-        <v>5</v>
+      <c r="P108" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11177,13 +11177,13 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11207,15 +11207,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28678101</v>
+        <v>28679487</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>TE NXT Toastmasters Club</t>
+          <t>o9 Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11256,28 +11256,28 @@
         </is>
       </c>
       <c r="P109" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q109" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q109" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R109" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="S109" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T109" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W109" s="10" t="n">
-        <v>5</v>
+      <c r="W109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
         <v>7</v>
@@ -11300,19 +11300,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28681070</v>
+        <v>28678101</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Talk Masters Toastmasters Club</t>
+          <t>TE NXT Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11352,32 +11352,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" s="9" t="n">
-        <v>0</v>
+      <c r="P110" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q110" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R110" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S110" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" s="9" t="n">
-        <v>0</v>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W110" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X110" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -11386,7 +11386,7 @@
         <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -11506,7 +11506,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11547,16 +11547,16 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123" s="10" t="n">
         <v>1</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>4</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13389,8 +13389,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P131" s="9" t="n">
-        <v>3</v>
+      <c r="P131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q131" s="10" t="n">
         <v>2</v>
@@ -13781,7 +13781,7 @@
         <v>0</v>
       </c>
       <c r="Q135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>0</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -15403,10 +15403,10 @@
         <v>11</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" s="8" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -15945,7 +15945,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16011,7 +16011,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -16176,7 +16176,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -16206,16 +16206,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -16224,7 +16224,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -16242,7 +16242,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -16296,25 +16296,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2.67</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -16323,7 +16323,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -16334,26 +16334,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>2</v>
@@ -16367,29 +16367,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -16400,14 +16400,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -16422,40 +16422,40 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -16466,29 +16466,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -16499,20 +16499,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -16521,7 +16521,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -16532,66 +16532,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>6</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I30"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>